--- a/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2508_W0076F0002T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.47663989414575</v>
+        <v>10.63995398279869</v>
       </c>
       <c r="D2" t="n">
-        <v>66.3263574864026</v>
+        <v>10.77803309154042</v>
       </c>
       <c r="E2" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F2" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>72.57050025982718</v>
+        <v>11.79270629222192</v>
       </c>
       <c r="D3" t="n">
-        <v>72.82078926243634</v>
+        <v>11.8333782551459</v>
       </c>
       <c r="E3" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F3" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.94779553816972</v>
+        <v>6.97901677495258</v>
       </c>
       <c r="D4" t="n">
-        <v>43.29267988647749</v>
+        <v>7.035060481552592</v>
       </c>
       <c r="E4" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F4" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.31999412840596</v>
+        <v>4.439499045865968</v>
       </c>
       <c r="D5" t="n">
-        <v>28.15460955853086</v>
+        <v>4.575124053261265</v>
       </c>
       <c r="E5" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F5" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.21784509991644</v>
+        <v>4.585399828736422</v>
       </c>
       <c r="D6" t="n">
-        <v>28.36909094044328</v>
+        <v>4.609977277822033</v>
       </c>
       <c r="E6" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F6" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>71.15674340333629</v>
+        <v>11.56297080304215</v>
       </c>
       <c r="D7" t="n">
-        <v>71.53661255102863</v>
+        <v>11.62469953954215</v>
       </c>
       <c r="E7" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F7" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.10026061717451</v>
+        <v>9.116292350290857</v>
       </c>
       <c r="D8" t="n">
-        <v>56.2857948481942</v>
+        <v>9.146441662831558</v>
       </c>
       <c r="E8" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F8" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.73884546876772</v>
+        <v>6.620062388674754</v>
       </c>
       <c r="D9" t="n">
-        <v>39.88372981193163</v>
+        <v>6.48110609443889</v>
       </c>
       <c r="E9" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F9" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.10130379185674</v>
+        <v>7.00396186617672</v>
       </c>
       <c r="D10" t="n">
-        <v>42.48675262032185</v>
+        <v>6.904097300802301</v>
       </c>
       <c r="E10" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F10" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>55.95099345124584</v>
+        <v>9.092036435827449</v>
       </c>
       <c r="D11" t="n">
-        <v>55.72705869525709</v>
+        <v>9.055647037979277</v>
       </c>
       <c r="E11" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F11" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.8349013736012</v>
+        <v>8.585671473210194</v>
       </c>
       <c r="D12" t="n">
-        <v>52.16103347551837</v>
+        <v>8.476167939771736</v>
       </c>
       <c r="E12" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F12" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>65.7067685065562</v>
+        <v>10.67734988231538</v>
       </c>
       <c r="D13" t="n">
-        <v>64.85314585666045</v>
+        <v>10.53863620170732</v>
       </c>
       <c r="E13" t="n">
-        <v>14.87470961063289</v>
+        <v>2.417140311727845</v>
       </c>
       <c r="F13" t="n">
-        <v>14.88202158677996</v>
+        <v>2.418328507851744</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
